--- a/hall/resources/sample/gameList.xlsx
+++ b/hall/resources/sample/gameList.xlsx
@@ -1,15 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
-  <fileVersion appName="xl" lastEdited="6" lowestEdited="6" rupBuild="14420"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="22527"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\workspace\gameserver\hall\resources\sample\"/>
     </mc:Choice>
   </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{48DF5DB0-F392-445E-9F43-C456933350DB}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="45" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15840"/>
+    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="GameListConfig" sheetId="1" r:id="rId1"/>
@@ -58,7 +59,7 @@
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <fonts count="3" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
@@ -411,12 +412,12 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:C5"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="2" max="2" width="14.125" customWidth="1"/>
-    <col min="3" max="3" width="8.75" customWidth="1"/>
+    <col min="3" max="3" width="20.125" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:3" x14ac:dyDescent="0.2">

--- a/hall/resources/sample/gameList.xlsx
+++ b/hall/resources/sample/gameList.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="22527"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="28827"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\workspace\gameserver\hall\resources\sample\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\java\project\hall\resources\sample\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{48DF5DB0-F392-445E-9F43-C456933350DB}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="45" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1F009080-D3C6-4A52-8369-3B6017A09241}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="7080" yWindow="1500" windowWidth="21600" windowHeight="11505" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="GameListConfig" sheetId="1" r:id="rId1"/>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="9" uniqueCount="8">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="10" uniqueCount="9">
   <si>
     <t>sid</t>
   </si>
@@ -53,6 +53,10 @@
   </si>
   <si>
     <t>状态  0.开启  1.维护  2.关闭</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>String</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -413,7 +417,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:C5"/>
+  <dimension ref="A1:C6"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="2" max="2" width="14.125" customWidth="1"/>
@@ -433,7 +437,9 @@
     </row>
     <row r="2" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A2" s="3"/>
-      <c r="B2" s="3"/>
+      <c r="B2" s="3" t="s">
+        <v>8</v>
+      </c>
       <c r="C2" s="2" t="s">
         <v>5</v>
       </c>
@@ -450,24 +456,29 @@
       </c>
     </row>
     <row r="4" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A4" s="1">
-        <v>100100</v>
-      </c>
-      <c r="B4" s="2" t="s">
-        <v>3</v>
-      </c>
-      <c r="C4" s="4">
-        <v>0</v>
-      </c>
+      <c r="A4" s="1"/>
+      <c r="B4" s="2"/>
+      <c r="C4" s="4"/>
     </row>
     <row r="5" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A5" s="1">
+        <v>100100</v>
+      </c>
+      <c r="B5" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="C5" s="4">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="6" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A6" s="1">
         <v>100200</v>
       </c>
-      <c r="B5" s="2" t="s">
+      <c r="B6" s="2" t="s">
         <v>4</v>
       </c>
-      <c r="C5" s="2">
+      <c r="C6" s="2">
         <v>2</v>
       </c>
     </row>

--- a/hall/resources/sample/gameList.xlsx
+++ b/hall/resources/sample/gameList.xlsx
@@ -5,15 +5,15 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\java\project\hall\resources\sample\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\workspace\gameserver\hall\resources\sample\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1F009080-D3C6-4A52-8369-3B6017A09241}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1451281D-2D5A-4A02-9D0F-55432EBA9AD9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="7080" yWindow="1500" windowWidth="21600" windowHeight="11505" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="34320" yWindow="4215" windowWidth="21600" windowHeight="11385" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="GameListConfig" sheetId="1" r:id="rId1"/>
+    <sheet name="GameList" sheetId="1" r:id="rId1"/>
   </sheets>
   <calcPr calcId="162913"/>
   <extLst>

--- a/hall/resources/sample/gameList.xlsx
+++ b/hall/resources/sample/gameList.xlsx
@@ -1,81 +1,76 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="28827"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:dbsheet="http://web.wps.cn/et/2021/dbsheet">
+  <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\workspace\gameserver\hall\resources\sample\"/>
-    </mc:Choice>
-  </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1451281D-2D5A-4A02-9D0F-55432EBA9AD9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="34320" yWindow="4215" windowWidth="21600" windowHeight="11385" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView windowWidth="28800" windowHeight="12375"/>
   </bookViews>
   <sheets>
     <sheet name="GameList" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="162913"/>
+  <calcPr calcId="191029"/>
   <extLst>
-    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
-      <x15:workbookPr chartTrackingRefBase="1"/>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
+        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
+      </xcalcf:calcFeatures>
     </ext>
   </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="10" uniqueCount="9">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="11" uniqueCount="9">
   <si>
-    <t>sid</t>
+    <t>id</t>
   </si>
   <si>
     <t>名称</t>
   </si>
   <si>
+    <t>状态  0.开启  1.维护  2.关闭</t>
+  </si>
+  <si>
+    <t>int</t>
+  </si>
+  <si>
+    <t>String</t>
+  </si>
+  <si>
     <t>name</t>
   </si>
   <si>
+    <t>status</t>
+  </si>
+  <si>
     <t>美元快递</t>
-    <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
     <t>森林人</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>int</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>status</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>状态  0.开启  1.维护  2.关闭</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>String</t>
-    <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="3" x14ac:knownFonts="1">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr9="http://schemas.microsoft.com/office/spreadsheetml/2016/revision9" mc:Ignorable="xr9">
+  <numFmts count="4">
+    <numFmt numFmtId="41" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;_ ;_ @_ "/>
+    <numFmt numFmtId="42" formatCode="_ &quot;￥&quot;* #,##0_ ;_ &quot;￥&quot;* \-#,##0_ ;_ &quot;￥&quot;* &quot;-&quot;_ ;_ @_ "/>
+    <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
+    <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
+  </numFmts>
+  <fonts count="22">
     <font>
       <sz val="11"/>
       <color theme="1"/>
       <name val="等线"/>
-      <family val="2"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="9"/>
-      <name val="等线"/>
-      <family val="3"/>
       <charset val="134"/>
       <scheme val="minor"/>
     </font>
@@ -83,20 +78,356 @@
       <sz val="10"/>
       <color theme="1"/>
       <name val="等线"/>
-      <family val="3"/>
       <charset val="134"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="等线"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF0000FF"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF800080"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFF0000"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="18"/>
+      <color theme="3"/>
+      <name val="等线"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <i/>
+      <sz val="11"/>
+      <color rgb="FF7F7F7F"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="15"/>
+      <color theme="3"/>
+      <name val="等线"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="13"/>
+      <color theme="3"/>
+      <name val="等线"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="3"/>
+      <name val="等线"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF3F3F76"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FF3F3F3F"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFA7D00"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFFFFFF"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFA7D00"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF006100"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF9C0006"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF9C6500"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="0"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
-  <fills count="2">
+  <fills count="33">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFCC"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFCC99"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF2F2F2"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA5A5A5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC6EFCE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFC7CE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFEB9C"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="2">
+  <borders count="10">
     <border>
       <left/>
       <right/>
@@ -119,9 +450,251 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color rgb="FFB2B2B2"/>
+      </left>
+      <right style="thin">
+        <color rgb="FFB2B2B2"/>
+      </right>
+      <top style="thin">
+        <color rgb="FFB2B2B2"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FFB2B2B2"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color theme="4"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color theme="4" tint="0.499984740745262"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF7F7F7F"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF7F7F7F"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF7F7F7F"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF7F7F7F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF3F3F3F"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF3F3F3F"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF3F3F3F"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF3F3F3F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="double">
+        <color rgb="FF3F3F3F"/>
+      </left>
+      <right style="double">
+        <color rgb="FF3F3F3F"/>
+      </right>
+      <top style="double">
+        <color rgb="FF3F3F3F"/>
+      </top>
+      <bottom style="double">
+        <color rgb="FF3F3F3F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="double">
+        <color rgb="FFFF8001"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color theme="4"/>
+      </top>
+      <bottom style="double">
+        <color theme="4"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
-  <cellStyleXfs count="1">
+  <cellStyleXfs count="49">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
+    <xf numFmtId="43" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="44" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="41" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="42" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="2" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="3" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="4" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="4" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="5" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
   </cellStyleXfs>
   <cellXfs count="5">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
@@ -131,24 +704,68 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
   </cellXfs>
-  <cellStyles count="1">
+  <cellStyles count="49">
     <cellStyle name="常规" xfId="0" builtinId="0"/>
+    <cellStyle name="千位分隔" xfId="1" builtinId="3"/>
+    <cellStyle name="货币" xfId="2" builtinId="4"/>
+    <cellStyle name="百分比" xfId="3" builtinId="5"/>
+    <cellStyle name="千位分隔[0]" xfId="4" builtinId="6"/>
+    <cellStyle name="货币[0]" xfId="5" builtinId="7"/>
+    <cellStyle name="超链接" xfId="6" builtinId="8"/>
+    <cellStyle name="已访问的超链接" xfId="7" builtinId="9"/>
+    <cellStyle name="注释" xfId="8" builtinId="10"/>
+    <cellStyle name="警告文本" xfId="9" builtinId="11"/>
+    <cellStyle name="标题" xfId="10" builtinId="15"/>
+    <cellStyle name="解释性文本" xfId="11" builtinId="53"/>
+    <cellStyle name="标题 1" xfId="12" builtinId="16"/>
+    <cellStyle name="标题 2" xfId="13" builtinId="17"/>
+    <cellStyle name="标题 3" xfId="14" builtinId="18"/>
+    <cellStyle name="标题 4" xfId="15" builtinId="19"/>
+    <cellStyle name="输入" xfId="16" builtinId="20"/>
+    <cellStyle name="输出" xfId="17" builtinId="21"/>
+    <cellStyle name="计算" xfId="18" builtinId="22"/>
+    <cellStyle name="检查单元格" xfId="19" builtinId="23"/>
+    <cellStyle name="链接单元格" xfId="20" builtinId="24"/>
+    <cellStyle name="汇总" xfId="21" builtinId="25"/>
+    <cellStyle name="好" xfId="22" builtinId="26"/>
+    <cellStyle name="差" xfId="23" builtinId="27"/>
+    <cellStyle name="适中" xfId="24" builtinId="28"/>
+    <cellStyle name="强调文字颜色 1" xfId="25" builtinId="29"/>
+    <cellStyle name="20% - 强调文字颜色 1" xfId="26" builtinId="30"/>
+    <cellStyle name="40% - 强调文字颜色 1" xfId="27" builtinId="31"/>
+    <cellStyle name="60% - 强调文字颜色 1" xfId="28" builtinId="32"/>
+    <cellStyle name="强调文字颜色 2" xfId="29" builtinId="33"/>
+    <cellStyle name="20% - 强调文字颜色 2" xfId="30" builtinId="34"/>
+    <cellStyle name="40% - 强调文字颜色 2" xfId="31" builtinId="35"/>
+    <cellStyle name="60% - 强调文字颜色 2" xfId="32" builtinId="36"/>
+    <cellStyle name="强调文字颜色 3" xfId="33" builtinId="37"/>
+    <cellStyle name="20% - 强调文字颜色 3" xfId="34" builtinId="38"/>
+    <cellStyle name="40% - 强调文字颜色 3" xfId="35" builtinId="39"/>
+    <cellStyle name="60% - 强调文字颜色 3" xfId="36" builtinId="40"/>
+    <cellStyle name="强调文字颜色 4" xfId="37" builtinId="41"/>
+    <cellStyle name="20% - 强调文字颜色 4" xfId="38" builtinId="42"/>
+    <cellStyle name="40% - 强调文字颜色 4" xfId="39" builtinId="43"/>
+    <cellStyle name="60% - 强调文字颜色 4" xfId="40" builtinId="44"/>
+    <cellStyle name="强调文字颜色 5" xfId="41" builtinId="45"/>
+    <cellStyle name="20% - 强调文字颜色 5" xfId="42" builtinId="46"/>
+    <cellStyle name="40% - 强调文字颜色 5" xfId="43" builtinId="47"/>
+    <cellStyle name="60% - 强调文字颜色 5" xfId="44" builtinId="48"/>
+    <cellStyle name="强调文字颜色 6" xfId="45" builtinId="49"/>
+    <cellStyle name="20% - 强调文字颜色 6" xfId="46" builtinId="50"/>
+    <cellStyle name="40% - 强调文字颜色 6" xfId="47" builtinId="51"/>
+    <cellStyle name="60% - 强调文字颜色 6" xfId="48" builtinId="52"/>
   </cellStyles>
-  <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
       <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
-    </ext>
-    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
-      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
     </ext>
   </extLst>
 </styleSheet>
@@ -197,7 +814,7 @@
     </a:clrScheme>
     <a:fontScheme name="Office">
       <a:majorFont>
-        <a:latin typeface="Calibri Light" panose="020F0302020204030204"/>
+        <a:latin typeface="Calibri Light"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
         <a:font script="Jpan" typeface="Yu Gothic Light"/>
@@ -232,7 +849,7 @@
         <a:font script="Geor" typeface="Sylfaen"/>
       </a:majorFont>
       <a:minorFont>
-        <a:latin typeface="Calibri" panose="020F0502020204030204"/>
+        <a:latin typeface="Calibri"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
         <a:font script="Jpan" typeface="Yu Gothic"/>
@@ -406,25 +1023,20 @@
     </a:fmtScheme>
   </a:themeElements>
   <a:objectDefaults/>
-  <a:extraClrSchemeLst/>
-  <a:extLst>
-    <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
-      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
-    </a:ext>
-  </a:extLst>
 </a:theme>
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
+  <sheetPr/>
   <dimension ref="A1:C6"/>
-  <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.25" outlineLevelRow="5" outlineLevelCol="2"/>
   <cols>
     <col min="2" max="2" width="14.125" customWidth="1"/>
     <col min="3" max="3" width="20.125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:3">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -432,59 +1044,61 @@
         <v>1</v>
       </c>
       <c r="C1" s="2" t="s">
-        <v>7</v>
+        <v>2</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A2" s="3"/>
+    <row r="2" spans="1:3">
+      <c r="A2" s="3" t="s">
+        <v>3</v>
+      </c>
       <c r="B2" s="3" t="s">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="C2" s="2" t="s">
-        <v>5</v>
+        <v>3</v>
       </c>
     </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:3">
       <c r="A3" s="1" t="s">
         <v>0</v>
       </c>
       <c r="B3" s="2" t="s">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="C3" s="2" t="s">
         <v>6</v>
       </c>
     </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:3">
       <c r="A4" s="1"/>
       <c r="B4" s="2"/>
       <c r="C4" s="4"/>
     </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:3">
       <c r="A5" s="1">
         <v>100100</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="C5" s="4">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:3">
       <c r="A6" s="1">
         <v>100200</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="C6" s="2">
         <v>2</v>
       </c>
     </row>
   </sheetData>
-  <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
+  <pageSetup paperSize="9" orientation="portrait"/>
+  <headerFooter/>
 </worksheet>
 </file>
--- a/hall/resources/sample/gameList.xlsx
+++ b/hall/resources/sample/gameList.xlsx
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="11" uniqueCount="9">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="12" uniqueCount="10">
   <si>
     <t>id</t>
   </si>
@@ -55,6 +55,9 @@
   <si>
     <t>森林人</t>
   </si>
+  <si>
+    <t>百家乐</t>
+  </si>
 </sst>
 </file>
 
@@ -66,7 +69,7 @@
     <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
   </numFmts>
-  <fonts count="22">
+  <fonts count="21">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -76,13 +79,6 @@
     </font>
     <font>
       <sz val="10"/>
-      <color theme="1"/>
-      <name val="等线"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
       <color theme="1"/>
       <name val="等线"/>
       <charset val="134"/>
@@ -551,148 +547,148 @@
   </borders>
   <cellStyleXfs count="49">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="43" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="44" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="9" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="41" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="42" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="43" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="44" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="41" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="42" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="2" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="2" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="3" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="4" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="4" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="5" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="3" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="4" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="4" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="5" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
@@ -1029,8 +1025,8 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:C6"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.25" outlineLevelRow="5" outlineLevelCol="2"/>
+  <dimension ref="A1:C7"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.25" outlineLevelRow="6" outlineLevelCol="2"/>
   <cols>
     <col min="2" max="2" width="14.125" customWidth="1"/>
     <col min="3" max="3" width="20.125" customWidth="1"/>
@@ -1096,6 +1092,17 @@
         <v>2</v>
       </c>
     </row>
+    <row r="7" spans="1:3">
+      <c r="A7">
+        <v>200500</v>
+      </c>
+      <c r="B7" t="s">
+        <v>9</v>
+      </c>
+      <c r="C7">
+        <v>0</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait"/>

--- a/hall/resources/sample/gameList.xlsx
+++ b/hall/resources/sample/gameList.xlsx
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="12" uniqueCount="10">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="14" uniqueCount="12">
   <si>
     <t>id</t>
   </si>
@@ -57,6 +57,12 @@
   </si>
   <si>
     <t>百家乐</t>
+  </si>
+  <si>
+    <t>飞禽走兽</t>
+  </si>
+  <si>
+    <t>豪车俱乐部</t>
   </si>
 </sst>
 </file>
@@ -1025,8 +1031,8 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:C7"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.25" outlineLevelRow="6" outlineLevelCol="2"/>
+  <dimension ref="A1:C9"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.25" outlineLevelCol="2"/>
   <cols>
     <col min="2" max="2" width="14.125" customWidth="1"/>
     <col min="3" max="3" width="20.125" customWidth="1"/>
@@ -1103,6 +1109,28 @@
         <v>0</v>
       </c>
     </row>
+    <row r="8" spans="1:3">
+      <c r="A8">
+        <v>200300</v>
+      </c>
+      <c r="B8" t="s">
+        <v>10</v>
+      </c>
+      <c r="C8">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="9" spans="1:3">
+      <c r="A9">
+        <v>200400</v>
+      </c>
+      <c r="B9" t="s">
+        <v>11</v>
+      </c>
+      <c r="C9">
+        <v>0</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait"/>

--- a/hall/resources/sample/gameList.xlsx
+++ b/hall/resources/sample/gameList.xlsx
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="14" uniqueCount="12">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="18" uniqueCount="16">
   <si>
     <t>id</t>
   </si>
@@ -63,6 +63,18 @@
   </si>
   <si>
     <t>豪车俱乐部</t>
+  </si>
+  <si>
+    <t>色碟</t>
+  </si>
+  <si>
+    <t>大小骰子</t>
+  </si>
+  <si>
+    <t>鱼虾蟹</t>
+  </si>
+  <si>
+    <t>三个骰子</t>
   </si>
 </sst>
 </file>
@@ -1031,7 +1043,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:C9"/>
+  <dimension ref="A1:C13"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.25" outlineLevelCol="2"/>
   <cols>
     <col min="2" max="2" width="14.125" customWidth="1"/>
@@ -1131,6 +1143,50 @@
         <v>0</v>
       </c>
     </row>
+    <row r="10" spans="1:3">
+      <c r="A10">
+        <v>200700</v>
+      </c>
+      <c r="B10" t="s">
+        <v>12</v>
+      </c>
+      <c r="C10">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="11" spans="1:3">
+      <c r="A11">
+        <v>200800</v>
+      </c>
+      <c r="B11" t="s">
+        <v>13</v>
+      </c>
+      <c r="C11">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="12" spans="1:3">
+      <c r="A12">
+        <v>200900</v>
+      </c>
+      <c r="B12" t="s">
+        <v>14</v>
+      </c>
+      <c r="C12">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="13" spans="1:3">
+      <c r="A13">
+        <v>200600</v>
+      </c>
+      <c r="B13" t="s">
+        <v>15</v>
+      </c>
+      <c r="C13">
+        <v>0</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait"/>

--- a/hall/resources/sample/gameList.xlsx
+++ b/hall/resources/sample/gameList.xlsx
@@ -1,16 +1,10 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="28925"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:dbsheet="http://web.wps.cn/et/2021/dbsheet">
+  <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\java\project\hall\resources\sample\"/>
-    </mc:Choice>
-  </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{897179A5-BAA5-4703-A7EF-48899E8BE885}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15990" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView windowWidth="28800" windowHeight="12375"/>
   </bookViews>
   <sheets>
     <sheet name="GameList" sheetId="1" r:id="rId1"/>
@@ -33,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="15" uniqueCount="13">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="21" uniqueCount="19">
   <si>
     <t>id</t>
   </si>
@@ -66,22 +60,43 @@
   </si>
   <si>
     <t>红黑大战</t>
-    <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <t>龙虎斗</t>
-    <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <t>德州扑克</t>
-    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>飞禽走兽</t>
+  </si>
+  <si>
+    <t>豪车俱乐部</t>
+  </si>
+  <si>
+    <t>三个骰子</t>
+  </si>
+  <si>
+    <t>色碟</t>
+  </si>
+  <si>
+    <t>大小骰子</t>
+  </si>
+  <si>
+    <t>鱼虾蟹</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="3" x14ac:knownFonts="1">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr9="http://schemas.microsoft.com/office/spreadsheetml/2016/revision9" mc:Ignorable="xr9">
+  <numFmts count="4">
+    <numFmt numFmtId="41" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;_ ;_ @_ "/>
+    <numFmt numFmtId="42" formatCode="_ &quot;￥&quot;* #,##0_ ;_ &quot;￥&quot;* \-#,##0_ ;_ &quot;￥&quot;* &quot;-&quot;_ ;_ @_ "/>
+    <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
+    <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
+  </numFmts>
+  <fonts count="23">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -93,27 +108,361 @@
       <sz val="10"/>
       <color theme="1"/>
       <name val="等线"/>
-      <family val="3"/>
       <charset val="134"/>
       <scheme val="minor"/>
     </font>
     <font>
-      <sz val="9"/>
-      <name val="等线"/>
-      <family val="3"/>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="微软雅黑"/>
       <charset val="134"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF000000"/>
+      <name val="微软雅黑"/>
+      <charset val="134"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF0000FF"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF800080"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFF0000"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="18"/>
+      <color theme="3"/>
+      <name val="等线"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <i/>
+      <sz val="11"/>
+      <color rgb="FF7F7F7F"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="15"/>
+      <color theme="3"/>
+      <name val="等线"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="13"/>
+      <color theme="3"/>
+      <name val="等线"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="3"/>
+      <name val="等线"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF3F3F76"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FF3F3F3F"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFA7D00"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFFFFFF"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFA7D00"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF006100"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF9C0006"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF9C6500"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="0"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="等线"/>
+      <charset val="0"/>
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="2">
+  <fills count="33">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFCC"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFCC99"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF2F2F2"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA5A5A5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC6EFCE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFC7CE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFEB9C"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="2">
+  <borders count="10">
     <border>
       <left/>
       <right/>
@@ -136,11 +485,253 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color rgb="FFB2B2B2"/>
+      </left>
+      <right style="thin">
+        <color rgb="FFB2B2B2"/>
+      </right>
+      <top style="thin">
+        <color rgb="FFB2B2B2"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FFB2B2B2"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color theme="4"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color theme="4" tint="0.499984740745262"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF7F7F7F"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF7F7F7F"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF7F7F7F"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF7F7F7F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF3F3F3F"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF3F3F3F"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF3F3F3F"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF3F3F3F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="double">
+        <color rgb="FF3F3F3F"/>
+      </left>
+      <right style="double">
+        <color rgb="FF3F3F3F"/>
+      </right>
+      <top style="double">
+        <color rgb="FF3F3F3F"/>
+      </top>
+      <bottom style="double">
+        <color rgb="FF3F3F3F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="double">
+        <color rgb="FFFF8001"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color theme="4"/>
+      </top>
+      <bottom style="double">
+        <color theme="4"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
-  <cellStyleXfs count="1">
+  <cellStyleXfs count="49">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
+    <xf numFmtId="43" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="44" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="41" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="42" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="2" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="3" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="4" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="4" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="5" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
   </cellStyleXfs>
-  <cellXfs count="9">
+  <cellXfs count="12">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
@@ -154,30 +745,83 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
+      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
     </xf>
   </cellXfs>
-  <cellStyles count="1">
+  <cellStyles count="49">
     <cellStyle name="常规" xfId="0" builtinId="0"/>
+    <cellStyle name="千位分隔" xfId="1" builtinId="3"/>
+    <cellStyle name="货币" xfId="2" builtinId="4"/>
+    <cellStyle name="百分比" xfId="3" builtinId="5"/>
+    <cellStyle name="千位分隔[0]" xfId="4" builtinId="6"/>
+    <cellStyle name="货币[0]" xfId="5" builtinId="7"/>
+    <cellStyle name="超链接" xfId="6" builtinId="8"/>
+    <cellStyle name="已访问的超链接" xfId="7" builtinId="9"/>
+    <cellStyle name="注释" xfId="8" builtinId="10"/>
+    <cellStyle name="警告文本" xfId="9" builtinId="11"/>
+    <cellStyle name="标题" xfId="10" builtinId="15"/>
+    <cellStyle name="解释性文本" xfId="11" builtinId="53"/>
+    <cellStyle name="标题 1" xfId="12" builtinId="16"/>
+    <cellStyle name="标题 2" xfId="13" builtinId="17"/>
+    <cellStyle name="标题 3" xfId="14" builtinId="18"/>
+    <cellStyle name="标题 4" xfId="15" builtinId="19"/>
+    <cellStyle name="输入" xfId="16" builtinId="20"/>
+    <cellStyle name="输出" xfId="17" builtinId="21"/>
+    <cellStyle name="计算" xfId="18" builtinId="22"/>
+    <cellStyle name="检查单元格" xfId="19" builtinId="23"/>
+    <cellStyle name="链接单元格" xfId="20" builtinId="24"/>
+    <cellStyle name="汇总" xfId="21" builtinId="25"/>
+    <cellStyle name="好" xfId="22" builtinId="26"/>
+    <cellStyle name="差" xfId="23" builtinId="27"/>
+    <cellStyle name="适中" xfId="24" builtinId="28"/>
+    <cellStyle name="强调文字颜色 1" xfId="25" builtinId="29"/>
+    <cellStyle name="20% - 强调文字颜色 1" xfId="26" builtinId="30"/>
+    <cellStyle name="40% - 强调文字颜色 1" xfId="27" builtinId="31"/>
+    <cellStyle name="60% - 强调文字颜色 1" xfId="28" builtinId="32"/>
+    <cellStyle name="强调文字颜色 2" xfId="29" builtinId="33"/>
+    <cellStyle name="20% - 强调文字颜色 2" xfId="30" builtinId="34"/>
+    <cellStyle name="40% - 强调文字颜色 2" xfId="31" builtinId="35"/>
+    <cellStyle name="60% - 强调文字颜色 2" xfId="32" builtinId="36"/>
+    <cellStyle name="强调文字颜色 3" xfId="33" builtinId="37"/>
+    <cellStyle name="20% - 强调文字颜色 3" xfId="34" builtinId="38"/>
+    <cellStyle name="40% - 强调文字颜色 3" xfId="35" builtinId="39"/>
+    <cellStyle name="60% - 强调文字颜色 3" xfId="36" builtinId="40"/>
+    <cellStyle name="强调文字颜色 4" xfId="37" builtinId="41"/>
+    <cellStyle name="20% - 强调文字颜色 4" xfId="38" builtinId="42"/>
+    <cellStyle name="40% - 强调文字颜色 4" xfId="39" builtinId="43"/>
+    <cellStyle name="60% - 强调文字颜色 4" xfId="40" builtinId="44"/>
+    <cellStyle name="强调文字颜色 5" xfId="41" builtinId="45"/>
+    <cellStyle name="20% - 强调文字颜色 5" xfId="42" builtinId="46"/>
+    <cellStyle name="40% - 强调文字颜色 5" xfId="43" builtinId="47"/>
+    <cellStyle name="60% - 强调文字颜色 5" xfId="44" builtinId="48"/>
+    <cellStyle name="强调文字颜色 6" xfId="45" builtinId="49"/>
+    <cellStyle name="20% - 强调文字颜色 6" xfId="46" builtinId="50"/>
+    <cellStyle name="40% - 强调文字颜色 6" xfId="47" builtinId="51"/>
+    <cellStyle name="60% - 强调文字颜色 6" xfId="48" builtinId="52"/>
   </cellStyles>
-  <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
       <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
-    </ext>
-    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
-      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
     </ext>
   </extLst>
 </styleSheet>
@@ -435,20 +1079,20 @@
     </a:fmtScheme>
   </a:themeElements>
   <a:objectDefaults/>
-  <a:extraClrSchemeLst/>
 </a:theme>
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:C10"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
+  <sheetPr/>
+  <dimension ref="A1:C16"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.25" outlineLevelCol="2"/>
   <cols>
     <col min="2" max="2" width="14.125" customWidth="1"/>
     <col min="3" max="3" width="20.125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:3">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -459,7 +1103,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:3">
       <c r="A2" s="3" t="s">
         <v>3</v>
       </c>
@@ -470,7 +1114,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:3">
       <c r="A3" s="1" t="s">
         <v>0</v>
       </c>
@@ -481,80 +1125,146 @@
         <v>6</v>
       </c>
     </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:3">
       <c r="A4" s="1"/>
       <c r="B4" s="2"/>
       <c r="C4" s="4"/>
     </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A5" s="1">
+    <row r="5" spans="1:3">
+      <c r="A5" s="5">
         <v>100100</v>
       </c>
-      <c r="B5" s="2" t="s">
+      <c r="B5" s="5" t="s">
         <v>7</v>
       </c>
-      <c r="C5" s="4">
+      <c r="C5" s="6">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A6" s="1">
+    <row r="6" spans="1:3">
+      <c r="A6" s="5">
         <v>100200</v>
       </c>
-      <c r="B6" s="2" t="s">
+      <c r="B6" s="5" t="s">
         <v>8</v>
       </c>
-      <c r="C6" s="2">
+      <c r="C6" s="5">
         <v>2</v>
       </c>
     </row>
-    <row r="7" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A7">
+    <row r="7" spans="1:3">
+      <c r="A7" s="7">
         <v>200500</v>
       </c>
-      <c r="B7" t="s">
+      <c r="B7" s="7" t="s">
         <v>9</v>
       </c>
-      <c r="C7">
+      <c r="C7" s="7">
         <v>0</v>
       </c>
     </row>
-    <row r="8" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A8" s="5">
+    <row r="8" spans="1:3">
+      <c r="A8" s="6">
         <v>200100</v>
       </c>
-      <c r="B8" s="4" t="s">
+      <c r="B8" s="6" t="s">
         <v>10</v>
       </c>
-      <c r="C8" s="4">
+      <c r="C8" s="6">
         <v>0</v>
       </c>
     </row>
-    <row r="9" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A9" s="5">
+    <row r="9" spans="1:3">
+      <c r="A9" s="6">
         <v>200101</v>
       </c>
-      <c r="B9" s="4" t="s">
+      <c r="B9" s="6" t="s">
         <v>11</v>
       </c>
-      <c r="C9" s="4">
+      <c r="C9" s="6">
         <v>0</v>
       </c>
     </row>
-    <row r="10" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A10" s="6">
+    <row r="10" spans="1:3">
+      <c r="A10" s="8">
         <v>300200</v>
       </c>
-      <c r="B10" s="7" t="s">
+      <c r="B10" s="9" t="s">
         <v>12</v>
       </c>
       <c r="C10" s="8">
         <v>0</v>
       </c>
     </row>
+    <row r="11" ht="16.5" spans="1:3">
+      <c r="A11" s="10">
+        <v>200300</v>
+      </c>
+      <c r="B11" s="10" t="s">
+        <v>13</v>
+      </c>
+      <c r="C11" s="7">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="12" ht="16.5" spans="1:3">
+      <c r="A12" s="10">
+        <v>200400</v>
+      </c>
+      <c r="B12" s="10" t="s">
+        <v>14</v>
+      </c>
+      <c r="C12" s="7">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="13" ht="16.5" spans="1:3">
+      <c r="A13" s="10">
+        <v>200600</v>
+      </c>
+      <c r="B13" s="10" t="s">
+        <v>15</v>
+      </c>
+      <c r="C13" s="7">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" ht="16.5" spans="1:3">
+      <c r="A14" s="10">
+        <v>200700</v>
+      </c>
+      <c r="B14" s="10" t="s">
+        <v>16</v>
+      </c>
+      <c r="C14" s="7">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15" ht="16.5" spans="1:3">
+      <c r="A15" s="10">
+        <v>200800</v>
+      </c>
+      <c r="B15" s="10" t="s">
+        <v>17</v>
+      </c>
+      <c r="C15" s="7">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16" ht="16.5" spans="1:3">
+      <c r="A16" s="10">
+        <v>200900</v>
+      </c>
+      <c r="B16" s="11" t="s">
+        <v>18</v>
+      </c>
+      <c r="C16" s="7">
+        <v>0</v>
+      </c>
+    </row>
   </sheetData>
-  <phoneticPr fontId="2" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait"/>
+  <headerFooter/>
 </worksheet>
 </file>
--- a/hall/resources/sample/gameList.xlsx
+++ b/hall/resources/sample/gameList.xlsx
@@ -1,16 +1,10 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="29029"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:dbsheet="http://web.wps.cn/et/2021/dbsheet">
+  <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\java\project\hall\resources\sample\"/>
-    </mc:Choice>
-  </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2DE9A71A-BAE6-42E3-B9F8-B6EFFF394C1F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="10485" yWindow="3000" windowWidth="15330" windowHeight="11040" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView windowWidth="27945" windowHeight="12375"/>
   </bookViews>
   <sheets>
     <sheet name="GameList" sheetId="1" r:id="rId1"/>
@@ -32,8 +26,42 @@
 </workbook>
 </file>
 
+<file path=xl/comments1.xml><?xml version="1.0" encoding="utf-8"?>
+<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <authors>
+    <author>Administrator</author>
+  </authors>
+  <commentList>
+    <comment ref="C1" authorId="0">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <rFont val="宋体"/>
+            <charset val="134"/>
+          </rPr>
+          <t>Administrator:</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <rFont val="宋体"/>
+            <charset val="134"/>
+          </rPr>
+          <t xml:space="preserve">
+0:大图标
+1：小图标
+</t>
+        </r>
+      </text>
+    </comment>
+  </commentList>
+</comments>
+</file>
+
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="22" uniqueCount="20">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="25" uniqueCount="22">
   <si>
     <t>id</t>
   </si>
@@ -41,6 +69,9 @@
     <t>名称</t>
   </si>
   <si>
+    <t>图标类型</t>
+  </si>
+  <si>
     <t>状态  0.开启  1.维护  2.关闭</t>
   </si>
   <si>
@@ -53,6 +84,9 @@
     <t>name</t>
   </si>
   <si>
+    <t>iconType</t>
+  </si>
+  <si>
     <t>status</t>
   </si>
   <si>
@@ -71,6 +105,9 @@
     <t>龙虎斗</t>
   </si>
   <si>
+    <t>21点</t>
+  </si>
+  <si>
     <t>德州扑克</t>
   </si>
   <si>
@@ -90,17 +127,19 @@
   </si>
   <si>
     <t>鱼虾蟹</t>
-  </si>
-  <si>
-    <t>21点</t>
-    <phoneticPr fontId="5" type="noConversion"/>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="6" x14ac:knownFonts="1">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr9="http://schemas.microsoft.com/office/spreadsheetml/2016/revision9" mc:Ignorable="xr9">
+  <numFmts count="4">
+    <numFmt numFmtId="41" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;_ ;_ @_ "/>
+    <numFmt numFmtId="42" formatCode="_ &quot;￥&quot;* #,##0_ ;_ &quot;￥&quot;* \-#,##0_ ;_ &quot;￥&quot;* &quot;-&quot;_ ;_ @_ "/>
+    <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
+    <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
+  </numFmts>
+  <fonts count="25">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -112,7 +151,6 @@
       <sz val="10"/>
       <color theme="1"/>
       <name val="等线"/>
-      <family val="3"/>
       <charset val="134"/>
       <scheme val="minor"/>
     </font>
@@ -120,41 +158,365 @@
       <sz val="11"/>
       <color theme="1"/>
       <name val="微软雅黑"/>
-      <family val="2"/>
       <charset val="134"/>
     </font>
     <font>
       <sz val="11"/>
       <color rgb="FF000000"/>
       <name val="微软雅黑"/>
-      <family val="2"/>
       <charset val="134"/>
     </font>
     <font>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF0000FF"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF800080"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFF0000"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="18"/>
+      <color theme="3"/>
+      <name val="等线"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <i/>
+      <sz val="11"/>
+      <color rgb="FF7F7F7F"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="15"/>
+      <color theme="3"/>
+      <name val="等线"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="13"/>
+      <color theme="3"/>
+      <name val="等线"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="3"/>
+      <name val="等线"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF3F3F76"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FF3F3F3F"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFA7D00"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFFFFFF"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFA7D00"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
       <sz val="11"/>
       <color theme="1"/>
       <name val="等线"/>
-      <family val="3"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF006100"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF9C0006"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF9C6500"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="0"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="9"/>
+      <name val="宋体"/>
       <charset val="134"/>
-      <scheme val="minor"/>
     </font>
     <font>
       <sz val="9"/>
-      <name val="等线"/>
-      <family val="3"/>
+      <name val="宋体"/>
       <charset val="134"/>
-      <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="2">
+  <fills count="33">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFCC"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFCC99"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF2F2F2"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA5A5A5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC6EFCE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFC7CE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFEB9C"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="2">
+  <borders count="10">
     <border>
       <left/>
       <right/>
@@ -177,9 +539,251 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color rgb="FFB2B2B2"/>
+      </left>
+      <right style="thin">
+        <color rgb="FFB2B2B2"/>
+      </right>
+      <top style="thin">
+        <color rgb="FFB2B2B2"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FFB2B2B2"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color theme="4"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color theme="4" tint="0.499984740745262"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF7F7F7F"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF7F7F7F"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF7F7F7F"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF7F7F7F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF3F3F3F"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF3F3F3F"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF3F3F3F"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF3F3F3F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="double">
+        <color rgb="FF3F3F3F"/>
+      </left>
+      <right style="double">
+        <color rgb="FF3F3F3F"/>
+      </right>
+      <top style="double">
+        <color rgb="FF3F3F3F"/>
+      </top>
+      <bottom style="double">
+        <color rgb="FF3F3F3F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="double">
+        <color rgb="FFFF8001"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color theme="4"/>
+      </top>
+      <bottom style="double">
+        <color theme="4"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
-  <cellStyleXfs count="1">
+  <cellStyleXfs count="49">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
+    <xf numFmtId="43" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="44" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="41" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="42" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="2" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="3" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="4" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="4" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="5" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
   </cellStyleXfs>
   <cellXfs count="11">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
@@ -204,27 +808,71 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
   </cellXfs>
-  <cellStyles count="1">
+  <cellStyles count="49">
     <cellStyle name="常规" xfId="0" builtinId="0"/>
+    <cellStyle name="千位分隔" xfId="1" builtinId="3"/>
+    <cellStyle name="货币" xfId="2" builtinId="4"/>
+    <cellStyle name="百分比" xfId="3" builtinId="5"/>
+    <cellStyle name="千位分隔[0]" xfId="4" builtinId="6"/>
+    <cellStyle name="货币[0]" xfId="5" builtinId="7"/>
+    <cellStyle name="超链接" xfId="6" builtinId="8"/>
+    <cellStyle name="已访问的超链接" xfId="7" builtinId="9"/>
+    <cellStyle name="注释" xfId="8" builtinId="10"/>
+    <cellStyle name="警告文本" xfId="9" builtinId="11"/>
+    <cellStyle name="标题" xfId="10" builtinId="15"/>
+    <cellStyle name="解释性文本" xfId="11" builtinId="53"/>
+    <cellStyle name="标题 1" xfId="12" builtinId="16"/>
+    <cellStyle name="标题 2" xfId="13" builtinId="17"/>
+    <cellStyle name="标题 3" xfId="14" builtinId="18"/>
+    <cellStyle name="标题 4" xfId="15" builtinId="19"/>
+    <cellStyle name="输入" xfId="16" builtinId="20"/>
+    <cellStyle name="输出" xfId="17" builtinId="21"/>
+    <cellStyle name="计算" xfId="18" builtinId="22"/>
+    <cellStyle name="检查单元格" xfId="19" builtinId="23"/>
+    <cellStyle name="链接单元格" xfId="20" builtinId="24"/>
+    <cellStyle name="汇总" xfId="21" builtinId="25"/>
+    <cellStyle name="好" xfId="22" builtinId="26"/>
+    <cellStyle name="差" xfId="23" builtinId="27"/>
+    <cellStyle name="适中" xfId="24" builtinId="28"/>
+    <cellStyle name="强调文字颜色 1" xfId="25" builtinId="29"/>
+    <cellStyle name="20% - 强调文字颜色 1" xfId="26" builtinId="30"/>
+    <cellStyle name="40% - 强调文字颜色 1" xfId="27" builtinId="31"/>
+    <cellStyle name="60% - 强调文字颜色 1" xfId="28" builtinId="32"/>
+    <cellStyle name="强调文字颜色 2" xfId="29" builtinId="33"/>
+    <cellStyle name="20% - 强调文字颜色 2" xfId="30" builtinId="34"/>
+    <cellStyle name="40% - 强调文字颜色 2" xfId="31" builtinId="35"/>
+    <cellStyle name="60% - 强调文字颜色 2" xfId="32" builtinId="36"/>
+    <cellStyle name="强调文字颜色 3" xfId="33" builtinId="37"/>
+    <cellStyle name="20% - 强调文字颜色 3" xfId="34" builtinId="38"/>
+    <cellStyle name="40% - 强调文字颜色 3" xfId="35" builtinId="39"/>
+    <cellStyle name="60% - 强调文字颜色 3" xfId="36" builtinId="40"/>
+    <cellStyle name="强调文字颜色 4" xfId="37" builtinId="41"/>
+    <cellStyle name="20% - 强调文字颜色 4" xfId="38" builtinId="42"/>
+    <cellStyle name="40% - 强调文字颜色 4" xfId="39" builtinId="43"/>
+    <cellStyle name="60% - 强调文字颜色 4" xfId="40" builtinId="44"/>
+    <cellStyle name="强调文字颜色 5" xfId="41" builtinId="45"/>
+    <cellStyle name="20% - 强调文字颜色 5" xfId="42" builtinId="46"/>
+    <cellStyle name="40% - 强调文字颜色 5" xfId="43" builtinId="47"/>
+    <cellStyle name="60% - 强调文字颜色 5" xfId="44" builtinId="48"/>
+    <cellStyle name="强调文字颜色 6" xfId="45" builtinId="49"/>
+    <cellStyle name="20% - 强调文字颜色 6" xfId="46" builtinId="50"/>
+    <cellStyle name="40% - 强调文字颜色 6" xfId="47" builtinId="51"/>
+    <cellStyle name="60% - 强调文字颜色 6" xfId="48" builtinId="52"/>
   </cellStyles>
-  <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
       <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
-    </ext>
-    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
-      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
     </ext>
   </extLst>
 </styleSheet>
@@ -482,20 +1130,20 @@
     </a:fmtScheme>
   </a:themeElements>
   <a:objectDefaults/>
-  <a:extraClrSchemeLst/>
 </a:theme>
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:C17"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
+  <sheetPr/>
+  <dimension ref="A1:D17"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.25" outlineLevelCol="3"/>
   <cols>
-    <col min="2" max="2" width="14.125" customWidth="1"/>
-    <col min="3" max="3" width="20.125" customWidth="1"/>
+    <col min="2" max="3" width="14.125" customWidth="1"/>
+    <col min="4" max="4" width="20.125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:4">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -505,180 +1153,230 @@
       <c r="C1" s="2" t="s">
         <v>2</v>
       </c>
-    </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="D1" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="2" spans="1:4">
       <c r="A2" s="3" t="s">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="B2" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="C2" s="2" t="s">
         <v>4</v>
       </c>
-      <c r="C2" s="2" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="D2" s="2" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="3" spans="1:4">
       <c r="A3" s="1" t="s">
         <v>0</v>
       </c>
       <c r="B3" s="2" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="C3" s="2" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.2">
+        <v>7</v>
+      </c>
+      <c r="D3" s="2" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="4" spans="1:4">
       <c r="A4" s="1"/>
       <c r="B4" s="2"/>
       <c r="C4" s="4"/>
-    </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="D4" s="4"/>
+    </row>
+    <row r="5" spans="1:4">
       <c r="A5" s="5">
         <v>100100</v>
       </c>
       <c r="B5" s="5" t="s">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="C5" s="6">
         <v>0</v>
       </c>
-    </row>
-    <row r="6" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="D5" s="6">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="6" spans="1:4">
       <c r="A6" s="5">
         <v>100200</v>
       </c>
       <c r="B6" s="5" t="s">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="C6" s="5">
+        <v>0</v>
+      </c>
+      <c r="D6" s="5">
         <v>2</v>
       </c>
     </row>
-    <row r="7" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:4">
       <c r="A7" s="7">
         <v>200500</v>
       </c>
       <c r="B7" s="7" t="s">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="C7" s="7">
         <v>0</v>
       </c>
-    </row>
-    <row r="8" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="D7" s="7">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="8" spans="1:4">
       <c r="A8" s="6">
         <v>200100</v>
       </c>
       <c r="B8" s="6" t="s">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="C8" s="6">
         <v>0</v>
       </c>
-    </row>
-    <row r="9" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="D8" s="6">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="9" spans="1:4">
       <c r="A9" s="6">
         <v>200101</v>
       </c>
       <c r="B9" s="6" t="s">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="C9" s="6">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="10" spans="1:3" x14ac:dyDescent="0.2">
+        <v>1</v>
+      </c>
+      <c r="D9" s="6">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="10" spans="1:4">
       <c r="A10" s="6">
         <v>300100</v>
       </c>
-      <c r="B10" s="10" t="s">
-        <v>19</v>
-      </c>
-      <c r="C10" s="6">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="11" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="B10" s="8" t="s">
+        <v>14</v>
+      </c>
+      <c r="C10" s="8">
+        <v>1</v>
+      </c>
+      <c r="D10" s="6">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="11" spans="1:4">
       <c r="A11" s="6">
         <v>300200</v>
       </c>
       <c r="B11" s="6" t="s">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="C11" s="6">
         <v>0</v>
       </c>
-    </row>
-    <row r="12" spans="1:3" ht="16.5" x14ac:dyDescent="0.3">
-      <c r="A12" s="8">
+      <c r="D11" s="6">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="12" ht="16.5" spans="1:4">
+      <c r="A12" s="9">
         <v>200300</v>
       </c>
-      <c r="B12" s="8" t="s">
-        <v>13</v>
-      </c>
-      <c r="C12" s="7">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="13" spans="1:3" ht="16.5" x14ac:dyDescent="0.3">
-      <c r="A13" s="8">
+      <c r="B12" s="9" t="s">
+        <v>16</v>
+      </c>
+      <c r="C12" s="9">
+        <v>1</v>
+      </c>
+      <c r="D12" s="7">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="13" ht="16.5" spans="1:4">
+      <c r="A13" s="9">
         <v>200400</v>
       </c>
-      <c r="B13" s="8" t="s">
-        <v>14</v>
-      </c>
-      <c r="C13" s="7">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="14" spans="1:3" ht="16.5" x14ac:dyDescent="0.3">
-      <c r="A14" s="8">
+      <c r="B13" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="C13" s="9">
+        <v>1</v>
+      </c>
+      <c r="D13" s="7">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" ht="16.5" spans="1:4">
+      <c r="A14" s="9">
         <v>200600</v>
       </c>
-      <c r="B14" s="8" t="s">
-        <v>15</v>
-      </c>
-      <c r="C14" s="7">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="15" spans="1:3" ht="16.5" x14ac:dyDescent="0.3">
-      <c r="A15" s="8">
+      <c r="B14" s="9" t="s">
+        <v>18</v>
+      </c>
+      <c r="C14" s="9">
+        <v>0</v>
+      </c>
+      <c r="D14" s="7">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15" ht="16.5" spans="1:4">
+      <c r="A15" s="9">
         <v>200700</v>
       </c>
-      <c r="B15" s="8" t="s">
-        <v>16</v>
-      </c>
-      <c r="C15" s="7">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="16" spans="1:3" ht="16.5" x14ac:dyDescent="0.3">
-      <c r="A16" s="8">
+      <c r="B15" s="9" t="s">
+        <v>19</v>
+      </c>
+      <c r="C15" s="9">
+        <v>0</v>
+      </c>
+      <c r="D15" s="7">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16" ht="16.5" spans="1:4">
+      <c r="A16" s="9">
         <v>200800</v>
       </c>
-      <c r="B16" s="8" t="s">
-        <v>17</v>
-      </c>
-      <c r="C16" s="7">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="17" spans="1:3" ht="16.5" x14ac:dyDescent="0.3">
-      <c r="A17" s="8">
+      <c r="B16" s="9" t="s">
+        <v>20</v>
+      </c>
+      <c r="C16" s="9">
+        <v>0</v>
+      </c>
+      <c r="D16" s="7">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="17" ht="16.5" spans="1:4">
+      <c r="A17" s="9">
         <v>200900</v>
       </c>
-      <c r="B17" s="9" t="s">
-        <v>18</v>
-      </c>
-      <c r="C17" s="7">
+      <c r="B17" s="10" t="s">
+        <v>21</v>
+      </c>
+      <c r="C17" s="10">
+        <v>1</v>
+      </c>
+      <c r="D17" s="7">
         <v>0</v>
       </c>
     </row>
   </sheetData>
-  <phoneticPr fontId="5" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait"/>
+  <headerFooter/>
+  <legacyDrawing r:id="rId2"/>
 </worksheet>
 </file>
--- a/hall/resources/sample/gameList.xlsx
+++ b/hall/resources/sample/gameList.xlsx
@@ -93,7 +93,7 @@
     <t>美元快递</t>
   </si>
   <si>
-    <t>森林人</t>
+    <t>超级明星</t>
   </si>
   <si>
     <t>百家乐</t>
@@ -1207,7 +1207,7 @@
     </row>
     <row r="6" spans="1:4">
       <c r="A6" s="5">
-        <v>100200</v>
+        <v>100300</v>
       </c>
       <c r="B6" s="5" t="s">
         <v>10</v>

--- a/hall/resources/sample/gameList.xlsx
+++ b/hall/resources/sample/gameList.xlsx
@@ -61,7 +61,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="25" uniqueCount="22">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="28" uniqueCount="25">
   <si>
     <t>id</t>
   </si>
@@ -94,6 +94,15 @@
   </si>
   <si>
     <t>超级明星</t>
+  </si>
+  <si>
+    <t>麻将胡了</t>
+  </si>
+  <si>
+    <t>财神</t>
+  </si>
+  <si>
+    <t>埃及艳后</t>
   </si>
   <si>
     <t>百家乐</t>
@@ -1136,7 +1145,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:D17"/>
+  <dimension ref="A1:D20"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.25" outlineLevelCol="3"/>
   <cols>
     <col min="2" max="3" width="14.125" customWidth="1"/>
@@ -1216,68 +1225,68 @@
         <v>0</v>
       </c>
       <c r="D6" s="5">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="7" spans="1:4">
-      <c r="A7" s="7">
-        <v>200500</v>
-      </c>
-      <c r="B7" s="7" t="s">
+      <c r="A7" s="6">
+        <v>100700</v>
+      </c>
+      <c r="B7" s="6" t="s">
         <v>11</v>
       </c>
-      <c r="C7" s="7">
-        <v>0</v>
-      </c>
-      <c r="D7" s="7">
+      <c r="C7" s="6">
+        <v>0</v>
+      </c>
+      <c r="D7" s="5">
         <v>0</v>
       </c>
     </row>
     <row r="8" spans="1:4">
       <c r="A8" s="6">
-        <v>200100</v>
+        <v>101200</v>
       </c>
       <c r="B8" s="6" t="s">
         <v>12</v>
       </c>
-      <c r="C8" s="6">
-        <v>0</v>
-      </c>
-      <c r="D8" s="6">
+      <c r="C8" s="5">
+        <v>0</v>
+      </c>
+      <c r="D8" s="5">
         <v>0</v>
       </c>
     </row>
     <row r="9" spans="1:4">
       <c r="A9" s="6">
-        <v>200101</v>
+        <v>101400</v>
       </c>
       <c r="B9" s="6" t="s">
         <v>13</v>
       </c>
       <c r="C9" s="6">
-        <v>1</v>
-      </c>
-      <c r="D9" s="6">
+        <v>0</v>
+      </c>
+      <c r="D9" s="5">
         <v>0</v>
       </c>
     </row>
     <row r="10" spans="1:4">
-      <c r="A10" s="6">
-        <v>300100</v>
-      </c>
-      <c r="B10" s="8" t="s">
+      <c r="A10" s="7">
+        <v>200500</v>
+      </c>
+      <c r="B10" s="7" t="s">
         <v>14</v>
       </c>
-      <c r="C10" s="8">
-        <v>1</v>
-      </c>
-      <c r="D10" s="6">
+      <c r="C10" s="7">
+        <v>0</v>
+      </c>
+      <c r="D10" s="7">
         <v>0</v>
       </c>
     </row>
     <row r="11" spans="1:4">
       <c r="A11" s="6">
-        <v>300200</v>
+        <v>200100</v>
       </c>
       <c r="B11" s="6" t="s">
         <v>15</v>
@@ -1289,57 +1298,57 @@
         <v>0</v>
       </c>
     </row>
-    <row r="12" ht="16.5" spans="1:4">
-      <c r="A12" s="9">
-        <v>200300</v>
-      </c>
-      <c r="B12" s="9" t="s">
+    <row r="12" spans="1:4">
+      <c r="A12" s="6">
+        <v>200101</v>
+      </c>
+      <c r="B12" s="6" t="s">
         <v>16</v>
       </c>
-      <c r="C12" s="9">
+      <c r="C12" s="6">
         <v>1</v>
       </c>
-      <c r="D12" s="7">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="13" ht="16.5" spans="1:4">
-      <c r="A13" s="9">
-        <v>200400</v>
-      </c>
-      <c r="B13" s="9" t="s">
+      <c r="D12" s="6">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="13" spans="1:4">
+      <c r="A13" s="6">
+        <v>300100</v>
+      </c>
+      <c r="B13" s="8" t="s">
         <v>17</v>
       </c>
-      <c r="C13" s="9">
+      <c r="C13" s="8">
         <v>1</v>
       </c>
-      <c r="D13" s="7">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="14" ht="16.5" spans="1:4">
-      <c r="A14" s="9">
-        <v>200600</v>
-      </c>
-      <c r="B14" s="9" t="s">
+      <c r="D13" s="6">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:4">
+      <c r="A14" s="6">
+        <v>300200</v>
+      </c>
+      <c r="B14" s="6" t="s">
         <v>18</v>
       </c>
-      <c r="C14" s="9">
-        <v>0</v>
-      </c>
-      <c r="D14" s="7">
+      <c r="C14" s="6">
+        <v>0</v>
+      </c>
+      <c r="D14" s="6">
         <v>0</v>
       </c>
     </row>
     <row r="15" ht="16.5" spans="1:4">
       <c r="A15" s="9">
-        <v>200700</v>
+        <v>200300</v>
       </c>
       <c r="B15" s="9" t="s">
         <v>19</v>
       </c>
       <c r="C15" s="9">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D15" s="7">
         <v>0</v>
@@ -1347,13 +1356,13 @@
     </row>
     <row r="16" ht="16.5" spans="1:4">
       <c r="A16" s="9">
-        <v>200800</v>
+        <v>200400</v>
       </c>
       <c r="B16" s="9" t="s">
         <v>20</v>
       </c>
       <c r="C16" s="9">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D16" s="7">
         <v>0</v>
@@ -1361,15 +1370,57 @@
     </row>
     <row r="17" ht="16.5" spans="1:4">
       <c r="A17" s="9">
+        <v>200600</v>
+      </c>
+      <c r="B17" s="9" t="s">
+        <v>21</v>
+      </c>
+      <c r="C17" s="9">
+        <v>0</v>
+      </c>
+      <c r="D17" s="7">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="18" ht="16.5" spans="1:4">
+      <c r="A18" s="9">
+        <v>200700</v>
+      </c>
+      <c r="B18" s="9" t="s">
+        <v>22</v>
+      </c>
+      <c r="C18" s="9">
+        <v>0</v>
+      </c>
+      <c r="D18" s="7">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="19" ht="16.5" spans="1:4">
+      <c r="A19" s="9">
+        <v>200800</v>
+      </c>
+      <c r="B19" s="9" t="s">
+        <v>23</v>
+      </c>
+      <c r="C19" s="9">
+        <v>0</v>
+      </c>
+      <c r="D19" s="7">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="20" ht="16.5" spans="1:4">
+      <c r="A20" s="9">
         <v>200900</v>
       </c>
-      <c r="B17" s="10" t="s">
-        <v>21</v>
-      </c>
-      <c r="C17" s="10">
+      <c r="B20" s="10" t="s">
+        <v>24</v>
+      </c>
+      <c r="C20" s="10">
         <v>1</v>
       </c>
-      <c r="D17" s="7">
+      <c r="D20" s="7">
         <v>0</v>
       </c>
     </row>
